--- a/artfynd/A 49366-2021 artfynd.xlsx
+++ b/artfynd/A 49366-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49366-2021 artfynd.xlsx
+++ b/artfynd/A 49366-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>96852555</v>
       </c>
       <c r="B2" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596678.9814853121</v>
+        <v>596680</v>
       </c>
       <c r="R2" t="n">
-        <v>6501043.77029999</v>
+        <v>6501044</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98662933</v>
+        <v>96852745</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,19 +804,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöberga, NO, Ög</t>
+          <t>Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596405.881049572</v>
+        <v>596406</v>
       </c>
       <c r="R3" t="n">
-        <v>6500969.299242577</v>
+        <v>6500969</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,29 +843,14 @@
           <t>Kvarsebo</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>E-Nor-0706</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +865,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -906,23 +873,14 @@
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>96852760</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596408.1341804054</v>
+        <v>596408</v>
       </c>
       <c r="R4" t="n">
-        <v>6500962.584958103</v>
+        <v>6500962</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,19 +951,9 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 49366-2021 artfynd.xlsx
+++ b/artfynd/A 49366-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852745</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,8 +992,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852760</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>